--- a/refs/heads/main/StructureDefinition-MessageHeaderRevisarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-MessageHeaderRevisarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
